--- a/ValueSet-ng-hiv-transfer-reason-vs.xlsx
+++ b/ValueSet-ng-hiv-transfer-reason-vs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
   <si>
     <t>Property</t>
   </si>
@@ -78,13 +78,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>NDHI (https://digitalhealth.gov.ng, emeka2015@gmail.com)</t>
-  </si>
-  <si>
-    <t>Nigeria Digital in Health Initiative. (lekeojewale@gmail.com(Work))</t>
-  </si>
-  <si>
-    <t>Nigeria Digital in Health Initiative. (emeka2015@gmail.com(Work))</t>
+    <t>NDHI (https://digitalhealth.gov.ng)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -257,7 +251,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -354,54 +348,38 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>25</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="B15" t="s" s="2">
         <v>27</v>
       </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
         <v>28</v>
       </c>
-      <c r="B16" s="2"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
+      <c r="B16" t="s" s="2">
         <v>29</v>
-      </c>
-      <c r="B17" s="2"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -420,28 +398,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
